--- a/data_u1/outcome_names.xlsx
+++ b/data_u1/outcome_names.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EE545A-D424-1B49-882A-50D3C2BC25F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9962D4BF-4392-514A-BE7A-051671C78A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18480" yWindow="-14860" windowWidth="26840" windowHeight="14860" xr2:uid="{D9DA298B-3661-D244-9246-A15BBBE54D2F}"/>
+    <workbookView xWindow="18480" yWindow="-17360" windowWidth="26840" windowHeight="14860" xr2:uid="{D9DA298B-3661-D244-9246-A15BBBE54D2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="78">
   <si>
     <t>adverse_event</t>
   </si>
@@ -261,6 +261,15 @@
   </si>
   <si>
     <t>Cognitive impairment (MMSE)</t>
+  </si>
+  <si>
+    <t>schizophrenia</t>
+  </si>
+  <si>
+    <t>Worsening or exacerbation of schizophrenia</t>
+  </si>
+  <si>
+    <t>Worsening of schizophrenia</t>
   </si>
 </sst>
 </file>
@@ -661,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12D15C2A-B84C-AD44-92F1-04D0189FED48}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.1640625" bestFit="1" customWidth="1"/>
@@ -1163,6 +1172,20 @@
         <v>28</v>
       </c>
     </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E34">
     <sortCondition ref="E3:E34"/>

--- a/data_u1/outcome_names.xlsx
+++ b/data_u1/outcome_names.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9962D4BF-4392-514A-BE7A-051671C78A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85542C39-0676-7148-861C-22E248C7DC23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18480" yWindow="-17360" windowWidth="26840" windowHeight="14860" xr2:uid="{D9DA298B-3661-D244-9246-A15BBBE54D2F}"/>
   </bookViews>

--- a/data_u1/outcome_names.xlsx
+++ b/data_u1/outcome_names.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85542C39-0676-7148-861C-22E248C7DC23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C824F9-C2AF-C64C-BD80-8E12FEE3803F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18480" yWindow="-17360" windowWidth="26840" windowHeight="14860" xr2:uid="{D9DA298B-3661-D244-9246-A15BBBE54D2F}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16260" xr2:uid="{D9DA298B-3661-D244-9246-A15BBBE54D2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -263,13 +263,13 @@
     <t>Cognitive impairment (MMSE)</t>
   </si>
   <si>
-    <t>schizophrenia</t>
-  </si>
-  <si>
-    <t>Worsening or exacerbation of schizophrenia</t>
-  </si>
-  <si>
-    <t>Worsening of schizophrenia</t>
+    <t>Worsening or exacerbation of psychosis</t>
+  </si>
+  <si>
+    <t>Worsening of psychosis</t>
+  </si>
+  <si>
+    <t>psychosis</t>
   </si>
 </sst>
 </file>
@@ -1174,13 +1174,13 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="E33">
         <v>29</v>
